--- a/002/002_SISMO_VIENTO_SALVADOR_R1.3_2.xlsx
+++ b/002/002_SISMO_VIENTO_SALVADOR_R1.3_2.xlsx
@@ -14356,7 +14356,6 @@
       </c>
       <c r="H90" s="1" t="str">
         <f>IF(G90&lt;0.3,"   &lt; 30%   No hay presiones internas","   &gt; 30%   Hay presiones internas")</f>
-        <v>   &gt; 30%   Hay presiones internas</v>
         <v xml:space="preserve">   &gt; 30%   Hay presiones internas</v>
       </c>
     </row>
